--- a/week-01/Kuppi Coffee Company Customer Satisfaction Survey.xlsx
+++ b/week-01/Kuppi Coffee Company Customer Satisfaction Survey.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0722D2-6F89-4CFB-91F5-6851B2C1AD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F7FDD-EB51-4634-B900-B1B2C4069461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5078" yWindow="293" windowWidth="16484" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="525" windowWidth="16485" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey_Responses" sheetId="1" r:id="rId1"/>
-    <sheet name="Rewards System" sheetId="2" r:id="rId2"/>
+    <sheet name="Loyalty_Rewards_Program" sheetId="5" r:id="rId2"/>
+    <sheet name="Menu Purchases" sheetId="4" r:id="rId3"/>
+    <sheet name="Recommendations" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="63">
   <si>
     <t>ID</t>
   </si>
@@ -196,13 +198,61 @@
     <t>Time to Complete</t>
   </si>
   <si>
-    <t>Row Labels</t>
-  </si>
-  <si>
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Count of Please rank the following rewards you would be most interested in (1 = most interest)</t>
+    <t>Interest in Loyalty Program</t>
+  </si>
+  <si>
+    <t>Type of Loyalty System</t>
+  </si>
+  <si>
+    <t>Count of System</t>
+  </si>
+  <si>
+    <t>Count of Interest</t>
+  </si>
+  <si>
+    <t>Reward Option</t>
+  </si>
+  <si>
+    <t>Free Specialty Drink</t>
+  </si>
+  <si>
+    <t>Kuppi Merch</t>
+  </si>
+  <si>
+    <t>Free Pastry/Baked Good</t>
+  </si>
+  <si>
+    <t>1 Point per $1 (Redeem for Free Food/Drink)</t>
+  </si>
+  <si>
+    <t>Free Milk Upgrade</t>
+  </si>
+  <si>
+    <t>Top Reward Ranking</t>
+  </si>
+  <si>
+    <t>Specialty coffee drinks (lattes, mochas, cappuccinos, iced drinks, etc.)</t>
+  </si>
+  <si>
+    <t>Menu Options</t>
+  </si>
+  <si>
+    <t>Count of Menu Options</t>
+  </si>
+  <si>
+    <t>Specialty non-coffee drinks (tea, chai, matcha, etc.)</t>
+  </si>
+  <si>
+    <t>Drip coffee</t>
+  </si>
+  <si>
+    <t>Pastries &amp; baked goods</t>
+  </si>
+  <si>
+    <t>Breakfast sandwiches</t>
   </si>
 </sst>
 </file>
@@ -210,10 +260,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -229,7 +287,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -237,21 +295,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -268,7 +336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -283,74 +351,295 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" pivotButton="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="42">
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -416,11 +705,11 @@
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -432,6 +721,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFBD9A7A"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -450,18 +744,42 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="107"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="7"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Kuppi Coffee Company Customer Satisfaction Survey.xlsx]Rewards System!PivotTable1</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Centaur Now Caption" panose="020F0502020204030204" pitchFamily="2" charset="0"/>
+              </a:rPr>
+              <a:t>Interest in a Rewards Program</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -475,11 +793,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -497,7 +815,7 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -553,7 +871,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -609,12 +927,754 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent5"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:pattFill prst="pct75">
+              <a:fgClr>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent5"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="20000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Total</c:v>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:shade val="76000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-83DF-4E90-A796-0346718A50A6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:tint val="77000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-83DF-4E90-A796-0346718A50A6}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="2"/>
+              <c:pt idx="0">
+                <c:v>Maybe, depending on the rewards</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Yes</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="2"/>
+              <c:pt idx="0">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>3</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-83DF-4E90-A796-0346718A50A6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="103"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="3"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="+mn-lt"/>
+                <a:cs typeface="Aparajita" panose="020B0502040204020203" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Rewards System Preference</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.19384779113640616"/>
+          <c:y val="5.1096201399262388E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
@@ -672,58 +1732,73 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>'Rewards System'!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Total</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:strRef>
-              <c:f>'Rewards System'!$A$2:$A$4</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Points-Based </c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Punch-Card </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:strLit>
+              <c:ptCount val="2"/>
+              <c:pt idx="0">
+                <c:v>Points-Based </c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Punch-Card </c:v>
+              </c:pt>
+            </c:strLit>
           </c:cat>
           <c:val>
-            <c:numRef>
-              <c:f>'Rewards System'!$B$2:$B$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="2"/>
+              <c:pt idx="0">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-2ED9-416E-9A3A-6076CCF8F3C5}"/>
+              <c16:uniqueId val="{00000000-4771-4DDC-A7B3-D7F3F05240D1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -735,13 +1810,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="176765504"/>
-        <c:axId val="176772704"/>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="157717951"/>
+        <c:axId val="157711231"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="176765504"/>
+        <c:axId val="157717951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -753,7 +1828,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -784,7 +1859,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="176772704"/>
+        <c:crossAx val="157711231"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -792,7 +1867,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="176772704"/>
+        <c:axId val="157711231"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -843,7 +1918,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="176765504"/>
+        <c:crossAx val="157717951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -927,26 +2002,11 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
+  <c:extLst/>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -959,12 +2019,43 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Kuppi Coffee Company Customer Satisfaction Survey.xlsx]Rewards System!PivotTable1</c:name>
-    <c:fmtId val="6"/>
-  </c:pivotSource>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="+mn-lt"/>
+              </a:rPr>
+              <a:t>Top Reward Ranking</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.29229855643044622"/>
+          <c:y val="5.0925925925925923E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -978,11 +2069,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -995,336 +2086,6 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="7"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="8"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-      </c:pivotFmt>
-    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:pieChart>
@@ -1334,11 +2095,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Rewards System'!$B$1</c:f>
+              <c:f>Loyalty_Rewards_Program!$B$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>Top Reward Ranking</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1353,11 +2114,17 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-26B7-4619-AD91-18CCF2769C73}"/>
+                <c16:uniqueId val="{00000001-B5AD-4B96-B9D4-D2ED3B4A9303}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1371,55 +2138,223 @@
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-26B7-4619-AD91-18CCF2769C73}"/>
+                <c16:uniqueId val="{00000003-B5AD-4B96-B9D4-D2ED3B4A9303}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-B5AD-4B96-B9D4-D2ED3B4A9303}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-B5AD-4B96-B9D4-D2ED3B4A9303}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-B5AD-4B96-B9D4-D2ED3B4A9303}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Rewards System'!$A$2:$A$4</c:f>
+              <c:f>Loyalty_Rewards_Program!$A$35:$A$39</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Points-Based </c:v>
+                  <c:v>Free Specialty Drink</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Punch-Card </c:v>
+                  <c:v>Free Pastry/Baked Good</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1 Point per $1 (Redeem for Free Food/Drink)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Free Milk Upgrade</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Kuppi Merch</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Rewards System'!$B$2:$B$4</c:f>
+              <c:f>Loyalty_Rewards_Program!$B$35:$B$39</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-26B7-4619-AD91-18CCF2769C73}"/>
+              <c16:uniqueId val="{00000000-A151-4A3C-A400-0D9767C3C4FA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="1"/>
         </c:dLbls>
@@ -1437,7 +2372,12 @@
       <c:legendPos val="r"/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -1450,9 +2390,9 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1467,23 +2407,32 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -1505,26 +2454,404 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="107"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="7"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Menu Purchases'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of Menu Options</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Menu Purchases'!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Drip coffee</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Specialty coffee drinks (lattes, mochas, cappuccinos, iced drinks, etc.)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Specialty non-coffee drinks (tea, chai, matcha, etc.)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Breakfast sandwiches</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Pastries &amp; baked goods</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Menu Purchases'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BEFA-48EA-8FD1-5C3F19CCC94A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:axId val="160590527"/>
+        <c:axId val="160591007"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="160590527"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="160591007"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="160591007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="95000"/>
+                      <a:lumOff val="5000"/>
+                      <a:alpha val="42000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                      <a:alpha val="36000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="160590527"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
+  <a:schemeClr val="accent5"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1564,48 +2891,615 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
   <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="340">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1616,7 +3510,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1629,7 +3523,7 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
@@ -1646,7 +3540,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -1662,7 +3556,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -1706,35 +3600,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1746,30 +3640,31 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1871,14 +3766,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -1968,20 +3857,20 @@
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -1994,6 +3883,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2025,7 +3925,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2034,14 +3934,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2095,184 +3994,245 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
         <a:solidFill>
           <a:schemeClr val="dk1">
             <a:lumMod val="25000"/>
             <a:lumOff val="75000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -2288,21 +4248,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2317,13 +4275,13 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
@@ -2336,17 +4294,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2355,12 +4313,12 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
@@ -2374,64 +4332,157 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="75000"/>
             <a:lumOff val="25000"/>
           </a:schemeClr>
@@ -2439,96 +4490,38 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
   </cs:seriesLine>
   <cs:title>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2537,14 +4530,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2553,9 +4545,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2573,9 +4565,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2586,11 +4578,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2598,14 +4595,578 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="218">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln>
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2614,27 +5175,29 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>100012</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3809999</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5502040-51DD-3F33-1FF3-FB9FEFC465F5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B3EDB33-38A9-4D57-A04D-79F5DF2E4CFC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2650,23 +5213,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>185738</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3890962</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>314326</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{312526B1-F71B-4F6B-9FC3-E9310AB25261}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0A37FDD-F34B-4901-860F-7612D04AB4D5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2686,6 +5249,180 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>211930</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>173831</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>250030</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>21431</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0E4F760-8DA5-F959-E229-0A781EF5D8FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>78581</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>69056</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>54768</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>97631</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F52D4D8-1599-FE07-3BFB-377F5C28AD7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>214313</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>128586</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5276850" cy="3192412"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68B18588-DF70-F474-2428-2E3D46D9A427}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="214313" y="128586"/>
+          <a:ext cx="5276850" cy="3192412"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BD9A7A"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Survey</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> results indicate that although Kuppi Coffee Company has a relatively new consumer base, the overall customer satisfaction rate is a five out of five, largely due to the in-store experience and anemities, which collective has an average rating of 4.6</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>Additonally, survey responses indicate that 60% of respondents said yes to a loyalty rewards program, with the remaining 40% expressiong conditional interest depending on the rewards offered. Overall, no respondents were opposed to the program, with 80% preferring a points-based system over a punch-card style loyalty program.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>Results indicate that the top preferred reward is a points-based redemption system where customers earn one point for every dollar spent, with the opprotuntiy to redeem points for free specialty drinks or food items. This aligns with pruchase trends, as specialty coffee drinks and breakfast sandwiches are the most frequently ordered items.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>To expand Kuppi's clientele and convert its new cosumer base into loyal customers, a points-based redeemtion loyalty program that targets specialtiy drinks and food purchases would likely yield the best resutls, as long as food and beveagre quality and the in-store expeirence remain high. </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2698,10 +5435,10 @@
     <cacheField name="ID" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
     </cacheField>
-    <cacheField name="Start time" numFmtId="166">
+    <cacheField name="Start time" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-08T22:58:41" maxDate="2026-04-10T01:07:40"/>
     </cacheField>
-    <cacheField name="Completion time" numFmtId="166">
+    <cacheField name="Completion time" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-08T23:01:26" maxDate="2026-04-10T01:08:48"/>
     </cacheField>
     <cacheField name="Time to Complete" numFmtId="45">
@@ -2750,7 +5487,10 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="8" maxValue="10"/>
     </cacheField>
     <cacheField name="Would you be interested in a loyalty/rewards program at Kuppi Coffee?" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="Maybe, depending on the rewards"/>
+        <s v="Yes"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Would you prefer a punch-card style reward or a points-based system? (Please select one)" numFmtId="0">
       <sharedItems count="2">
@@ -2791,7 +5531,7 @@
     <s v="Very Satisfied"/>
     <x v="0"/>
     <n v="9"/>
-    <s v="Maybe, depending on the rewards"/>
+    <x v="0"/>
     <x v="0"/>
     <s v="Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Earn a free specialty drink after every 10 drink purchases;Earn a free pastry or baked good after every 6 food purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;"/>
     <s v="Add more deals and discounts"/>
@@ -2812,7 +5552,7 @@
     <s v="Satisfied"/>
     <x v="1"/>
     <n v="8"/>
-    <s v="Maybe, depending on the rewards"/>
+    <x v="0"/>
     <x v="0"/>
     <s v="Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty drink after every 10 drink purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;"/>
     <s v="No"/>
@@ -2833,7 +5573,7 @@
     <s v="Very Satisfied"/>
     <x v="0"/>
     <n v="10"/>
-    <s v="Yes"/>
+    <x v="1"/>
     <x v="0"/>
     <s v="Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;Earn a free specialty drink after every 10 drink purchases;Earn a free pastry or baked good after every 6 food purchases;"/>
     <s v="N/A"/>
@@ -2854,7 +5594,7 @@
     <s v="Very Satisfied"/>
     <x v="1"/>
     <n v="9"/>
-    <s v="Yes"/>
+    <x v="1"/>
     <x v="0"/>
     <s v="Earn a free specialty drink after every 10 drink purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;"/>
     <s v="No additional comments or concerns at this time, but the next time I'm in town, I'm definitely coming here. "/>
@@ -2875,7 +5615,7 @@
     <s v="Very Satisfied"/>
     <x v="0"/>
     <n v="10"/>
-    <s v="Yes"/>
+    <x v="1"/>
     <x v="1"/>
     <s v="Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty drink after every 10 drink purchases;Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);"/>
     <s v="N/A"/>
@@ -2884,12 +5624,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE3F55F9-1728-4979-9E5D-3F91AF54AAA6}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F16C2FB4-748C-49E0-B7CB-D09E4EAB8E0C}" name="PivotTable18" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22" rowHeaderCaption="Type of Loyalty System">
+  <location ref="A17:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField numFmtId="45" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2946,8 +5686,41 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Please rank the following rewards you would be most interested in (1 = most interest)" fld="17" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Count of System" fld="17" subtotal="count" baseField="16" baseItem="0"/>
   </dataFields>
+  <formats count="9">
+    <format dxfId="12">
+      <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="16" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
   <chartFormats count="4">
     <chartFormat chart="0" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -2958,7 +5731,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="6" format="6" series="1">
+    <chartFormat chart="12" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -2967,26 +5740,141 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="6" format="7">
+    <chartFormat chart="13" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="16" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="6" format="8">
+    <chartFormat chart="15" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
+        <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
           </reference>
-          <reference field="16" count="1" selected="0">
-            <x v="1"/>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E202CC2-66D6-43A3-8832-B82793539121}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Interest in Loyalty Program">
+  <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="45" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="15"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Interest" fld="0" subtotal="count" baseField="15" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="21">
+      <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="15" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="18">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="15" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -3005,49 +5893,71 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:S7" totalsRowCount="1" headerRowDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:S7" totalsRowCount="1" headerRowDxfId="41">
   <autoFilter ref="A1:S6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="37" totalsRowDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="36" totalsRowDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="35" totalsRowDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{574F5E68-45C2-4C0B-B4DD-7D02BE97E8A1}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="34" totalsRowDxfId="15">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="39" totalsRowDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="38" totalsRowDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{574F5E68-45C2-4C0B-B4DD-7D02BE97E8A1}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="1">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(D2:D6)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="33" totalsRowDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How often do you visit Kuppi Coffee?" dataDxfId="32" totalsRowDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How satisfied are you with your overall experience at our cafe? (1 = Very Dissatisfied → 5 = Very Satisfied)" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="12">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How often do you visit Kuppi Coffee?" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How satisfied are you with your overall experience at our cafe? (1 = Very Dissatisfied → 5 = Very Satisfied)" totalsRowFunction="custom" dataDxfId="34">
       <totalsRowFormula>AVERAGE(G2:G6)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Which of the following do you typically order at Kuppi Coffee? (select all that apply)" dataDxfId="30" totalsRowDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Staff Friendliness" totalsRowFunction="custom" dataDxfId="29" totalsRowDxfId="10">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Which of the following do you typically order at Kuppi Coffee? (select all that apply)" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Staff Friendliness" totalsRowFunction="custom" dataDxfId="32" totalsRowDxfId="0">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(I2:I6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Speed of Service" totalsRowFunction="custom" dataDxfId="28" totalsRowDxfId="9">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Speed of Service" totalsRowFunction="custom" dataDxfId="31">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(J2:J6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Cleanliness" totalsRowFunction="custom" dataDxfId="27" totalsRowDxfId="8">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Cleanliness" totalsRowFunction="custom" dataDxfId="30">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(K2:K6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Wi-Fi Quality" totalsRowFunction="custom" dataDxfId="26" totalsRowDxfId="7">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Wi-Fi Quality" totalsRowFunction="custom" dataDxfId="29">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(L2:L6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Seating Comfort" totalsRowFunction="custom" dataDxfId="25" totalsRowDxfId="6">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Seating Comfort" totalsRowFunction="custom" dataDxfId="28">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(M2:M6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Food &amp; Drink Quality" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="5">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Food &amp; Drink Quality" totalsRowFunction="custom" dataDxfId="27">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(N2:N6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="How likely are you to recommend Kuppi Coffee to someone? (1 = Not at all likely → 10 = Extremely likely)" dataDxfId="23" totalsRowDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Would you be interested in a loyalty/rewards program at Kuppi Coffee?" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="3">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="How likely are you to recommend Kuppi Coffee to someone? (1 = Not at all likely → 10 = Extremely likely)" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Would you be interested in a loyalty/rewards program at Kuppi Coffee?" totalsRowFunction="custom" dataDxfId="25">
       <totalsRowFormula>COUNTIF(P2:P6, "Maybe, depending on the rewards")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Would you prefer a punch-card style reward or a points-based system? (Please select one)" dataDxfId="21" totalsRowDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Please rank the following rewards you would be most interested in (1 = most interest)" dataDxfId="20" totalsRowDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Any additional comments or concerns?" dataDxfId="19" totalsRowDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Would you prefer a punch-card style reward or a points-based system? (Please select one)" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Please rank the following rewards you would be most interested in (1 = most interest)" dataDxfId="23"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Any additional comments or concerns?" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{771977B7-73CE-4534-915A-3AE51AF0ECB0}" name="Table2" displayName="Table2" ref="A34:B39" totalsRowShown="0">
+  <autoFilter ref="A34:B39" xr:uid="{771977B7-73CE-4534-915A-3AE51AF0ECB0}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{AC3C676E-B4E2-4EDA-A266-F27991454E89}" name="Reward Option"/>
+    <tableColumn id="2" xr3:uid="{1E99A44D-F924-46C4-9AAA-F2067EF6E962}" name="Top Reward Ranking"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9B3D2ACC-D4F5-4E6F-A441-36EB32A96316}" name="Table25" displayName="Table25" ref="A1:B6" totalsRowShown="0">
+  <autoFilter ref="A1:B6" xr:uid="{9B3D2ACC-D4F5-4E6F-A441-36EB32A96316}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{518C367B-86D5-49B8-9782-763979A2E6FA}" name="Menu Options"/>
+    <tableColumn id="2" xr3:uid="{793A1FA4-250C-428D-88BB-EFF9362D045C}" name="Count of Menu Options"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3348,7 +6258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.6640625" customWidth="1"/>
@@ -3365,411 +6275,439 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="18" t="s">
+      <c r="S1" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="16">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="9">
         <v>46120.957418981503</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="9">
         <v>46120.959328703699</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="11">
         <f>C2-B2</f>
         <v>1.9097221957053989E-3</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="10">
         <v>5</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="10">
         <v>9</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="Q2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="S2" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="16">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="9">
         <v>46121.4062962963</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="9">
         <v>46121.408391203702</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="11">
         <f t="shared" ref="D3:D6" si="0">C3-B3</f>
         <v>2.0949074023519643E-3</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="10">
         <v>5</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="10">
         <v>8</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="Q3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="A4" s="16">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="9">
         <v>46121.408344907402</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="9">
         <v>46121.409629629597</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="11">
         <f t="shared" si="0"/>
         <v>1.2847221951233223E-3</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="10">
         <v>5</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="N4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="10">
         <v>10</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="Q4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="R4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="S4" s="10" t="s">
+      <c r="S4" s="7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="16">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="9">
         <v>46121.488275463002</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="9">
         <v>46121.4901157407</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="11">
         <f t="shared" si="0"/>
         <v>1.8402776986476965E-3</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="10">
         <v>5</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="13" t="s">
+      <c r="N5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="10">
         <v>9</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="Q5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="16">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="9">
         <v>46122.046990740702</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="9">
         <v>46122.0477777778</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="11">
         <f t="shared" si="0"/>
         <v>7.8703709732508287E-4</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="10">
         <v>5</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="10">
         <v>10</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="Q6" s="13" t="s">
+      <c r="Q6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="R6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="S6" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="3">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="2">
         <f>AVERAGE(D2:D6)</f>
         <v>1.5833333178306929E-3</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
+      <c r="G7">
         <f>AVERAGE(G2:G6)</f>
         <v>5</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="4" cm="1">
+      <c r="I7" s="3" cm="1">
         <f t="array" ref="I7">AVERAGE(_xlfn.SWITCH(I2:I6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="J7" s="1" cm="1">
+      <c r="J7" cm="1">
         <f t="array" ref="J7">AVERAGE(_xlfn.SWITCH(J2:J6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="K7" s="1" cm="1">
+      <c r="K7" cm="1">
         <f t="array" ref="K7">AVERAGE(_xlfn.SWITCH(K2:K6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</f>
         <v>4.8</v>
       </c>
-      <c r="L7" s="1" cm="1">
+      <c r="L7" cm="1">
         <f t="array" ref="L7">AVERAGE(_xlfn.SWITCH(L2:L6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="M7" s="1" cm="1">
+      <c r="M7" cm="1">
         <f t="array" ref="M7">AVERAGE(_xlfn.SWITCH(M2:M6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</f>
         <v>4.8</v>
       </c>
-      <c r="N7" s="1" cm="1">
+      <c r="N7" cm="1">
         <f t="array" ref="N7">AVERAGE(_xlfn.SWITCH(N2:N6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</f>
         <v>4.5999999999999996</v>
       </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1">
+      <c r="P7">
         <f>COUNTIF(P2:P6, "Maybe, depending on the rewards")</f>
         <v>2</v>
       </c>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I9">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I10">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I11">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I12">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I13">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I14">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I15" s="24">
+        <f>AVERAGE(I9:I14)</f>
+        <v>4.6000000000000005</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3781,48 +6719,217 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2684A6-2A33-40A3-B901-8836FED50976}">
-  <dimension ref="A1:B4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4AEBE3-C606-4B13-8367-078B9EF83811}">
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="79.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.3984375" customWidth="1"/>
+    <col min="2" max="2" width="17.9296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35">
+        <f>COUNTIF(Survey_Responses!R2:R6, "Earn a free specialty drink after every 10 drink purchases*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36">
+        <f>COUNTIF(Survey_Responses!R2:R6, "Earn a free pastry or baked good after every 6 food purchases*")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37">
+        <f>COUNTIF(Survey_Responses!R2:R6, "Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice*")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38">
+        <f>COUNTIF(Survey_Responses!R2:R6, "Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39">
+        <f>COUNTIF(Survey_Responses!R2:R6, "Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags)*")</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B574709F-6E12-4BCB-BC98-2A74DB8E28D2}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
-        <v>44</v>
+      <c r="A1" t="s">
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="1">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2">
+        <f>COUNTIF(Survey_Responses!H2:H6, "*Drip Coffee*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="57" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="16">
+        <f>COUNTIF(Survey_Responses!H2:H6, "*Specialty coffee drinks (lattes, mochas, cappuccinos, iced drinks, etc.)*")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="4" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4">
+        <f>COUNTIF(Survey_Responses!H2:H6, "*Specialty non-coffee drinks (tea, chai, matcha, etc.)*")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="1">
-        <v>5</v>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5">
+        <f>COUNTIF(Survey_Responses!H2:H6, "*Breakfast sandwiches*")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6">
+        <f>COUNTIF(Survey_Responses!H2:H6, "*Pastries &amp; baked goods*")</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D15E29-8D0E-48CB-B3C9-5E948B747485}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/week-01/Kuppi Coffee Company Customer Satisfaction Survey.xlsx
+++ b/week-01/Kuppi Coffee Company Customer Satisfaction Survey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F7FDD-EB51-4634-B900-B1B2C4069461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FEB60B-6B5F-4C98-9442-D5FA6DC64DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="525" windowWidth="16485" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="525" windowWidth="16485" windowHeight="12060" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey_Responses" sheetId="1" r:id="rId1"/>
@@ -384,18 +384,6 @@
   </cellStyles>
   <dxfs count="42">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color indexed="64"/>
@@ -681,6 +669,9 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -702,11 +693,20 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="28" formatCode="mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="28" formatCode="mm:ss"/>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
@@ -5338,7 +5338,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>128586</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5276850" cy="3192412"/>
+    <xdr:ext cx="5276850" cy="3536866"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
@@ -5353,7 +5353,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="214313" y="128586"/>
-          <a:ext cx="5276850" cy="3192412"/>
+          <a:ext cx="5276850" cy="3536866"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5382,41 +5382,90 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Survey</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> results indicate that although Kuppi Coffee Company has a relatively new consumer base, the overall customer satisfaction rate is a five out of five, largely due to the in-store experience and anemities, which collective has an average rating of 4.6</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Survey results indicate that although Kuppi Coffee Company has a relatively new consumer base, the overall customer satisfaction rate is a five out of five, largely due to the in-store experience and amenities, which collective has an average rating of 4.6</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>Additonally, survey responses indicate that 60% of respondents said yes to a loyalty rewards program, with the remaining 40% expressiong conditional interest depending on the rewards offered. Overall, no respondents were opposed to the program, with 80% preferring a points-based system over a punch-card style loyalty program.</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Additionally, survey responses indicate that 60% of respondents said yes to a loyalty rewards program, with the remaining 40% expressing conditional interest depending on the rewards offered. Overall, no respondents were opposed to the program, with 80% preferring a points-based system over a punch-card style loyalty program.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>Results indicate that the top preferred reward is a points-based redemption system where customers earn one point for every dollar spent, with the opprotuntiy to redeem points for free specialty drinks or food items. This aligns with pruchase trends, as specialty coffee drinks and breakfast sandwiches are the most frequently ordered items.</a:t>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Results indicate that the top preferred reward is a points-based redemption system where customers earn one point for every dollar spent, with the opportunity to redeem points for free specialty drinks or food items. This aligns with purchase trends, as specialty coffee drinks and breakfast sandwiches are the most frequently ordered items.</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
+          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t>To expand Kuppi's clientele and convert its new cosumer base into loyal customers, a points-based redeemtion loyalty program that targets specialtiy drinks and food purchases would likely yield the best resutls, as long as food and beveagre quality and the in-store expeirence remain high. </a:t>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>To expand Kuppi's clientele and convert its new consumer base into loyal customers, a points-based redemption loyalty program that targets specialty drinks and food purchases would likely yield the best results, as long as food and beverage quality and the in-store experience remain high. </a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" b="0">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:br>
+            <a:rPr lang="en-US"/>
+          </a:br>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -5689,35 +5738,35 @@
     <dataField name="Count of System" fld="17" subtotal="count" baseField="16" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="12">
+    <format dxfId="8">
       <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="7">
       <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="6">
       <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="5">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="3">
       <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="16" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5822,13 +5871,13 @@
     <dataField name="Count of Interest" fld="0" subtotal="count" baseField="15" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="21">
+    <format dxfId="17">
       <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="15" count="1">
@@ -5837,26 +5886,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="14">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="13">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="12">
       <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="15" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5897,43 +5946,43 @@
   <autoFilter ref="A1:S6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="39" totalsRowDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="38" totalsRowDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{574F5E68-45C2-4C0B-B4DD-7D02BE97E8A1}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="1">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="21" xr3:uid="{574F5E68-45C2-4C0B-B4DD-7D02BE97E8A1}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="34">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(D2:D6)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How often do you visit Kuppi Coffee?" dataDxfId="35"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How satisfied are you with your overall experience at our cafe? (1 = Very Dissatisfied → 5 = Very Satisfied)" totalsRowFunction="custom" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How often do you visit Kuppi Coffee?" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How satisfied are you with your overall experience at our cafe? (1 = Very Dissatisfied → 5 = Very Satisfied)" totalsRowFunction="custom" dataDxfId="31">
       <totalsRowFormula>AVERAGE(G2:G6)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Which of the following do you typically order at Kuppi Coffee? (select all that apply)" dataDxfId="33"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Staff Friendliness" totalsRowFunction="custom" dataDxfId="32" totalsRowDxfId="0">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Which of the following do you typically order at Kuppi Coffee? (select all that apply)" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Staff Friendliness" totalsRowFunction="custom" dataDxfId="29" totalsRowDxfId="28">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(I2:I6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Speed of Service" totalsRowFunction="custom" dataDxfId="31">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Speed of Service" totalsRowFunction="custom" dataDxfId="27">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(J2:J6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Cleanliness" totalsRowFunction="custom" dataDxfId="30">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Cleanliness" totalsRowFunction="custom" dataDxfId="26">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(K2:K6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Wi-Fi Quality" totalsRowFunction="custom" dataDxfId="29">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Wi-Fi Quality" totalsRowFunction="custom" dataDxfId="25">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(L2:L6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Seating Comfort" totalsRowFunction="custom" dataDxfId="28">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Seating Comfort" totalsRowFunction="custom" dataDxfId="24">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(M2:M6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Food &amp; Drink Quality" totalsRowFunction="custom" dataDxfId="27">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Food &amp; Drink Quality" totalsRowFunction="custom" dataDxfId="23">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(N2:N6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="How likely are you to recommend Kuppi Coffee to someone? (1 = Not at all likely → 10 = Extremely likely)" dataDxfId="26"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Would you be interested in a loyalty/rewards program at Kuppi Coffee?" totalsRowFunction="custom" dataDxfId="25">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="How likely are you to recommend Kuppi Coffee to someone? (1 = Not at all likely → 10 = Extremely likely)" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Would you be interested in a loyalty/rewards program at Kuppi Coffee?" totalsRowFunction="custom" dataDxfId="21">
       <totalsRowFormula>COUNTIF(P2:P6, "Maybe, depending on the rewards")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Would you prefer a punch-card style reward or a points-based system? (Please select one)" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Please rank the following rewards you would be most interested in (1 = most interest)" dataDxfId="23"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Any additional comments or concerns?" dataDxfId="22"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Would you prefer a punch-card style reward or a points-based system? (Please select one)" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Please rank the following rewards you would be most interested in (1 = most interest)" dataDxfId="19"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Any additional comments or concerns?" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/week-01/Kuppi Coffee Company Customer Satisfaction Survey.xlsx
+++ b/week-01/Kuppi Coffee Company Customer Satisfaction Survey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FEB60B-6B5F-4C98-9442-D5FA6DC64DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D715802-FD2B-4F9F-AD7B-E1EBC7A83B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="525" windowWidth="16485" windowHeight="12060" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1208" yWindow="442" windowWidth="20025" windowHeight="12061" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey_Responses" sheetId="1" r:id="rId1"/>
@@ -5382,30 +5382,28 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
+            <a:rPr lang="en-US">
               <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Survey results indicate that although Kuppi Coffee Company has a relatively new consumer base, the overall customer satisfaction rate is a five out of five, largely due to the in-store experience and amenities, which collective has an average rating of 4.6</a:t>
+            <a:t>Survey results indicate that although Kuppi Coffee Company has a relatively new consumer base, the overall customer satisfaction rate is a five out of five, largely due to the in-store experience and amenities,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" baseline="0">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> which collectively has an average rating of 4.6</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr rtl="0"/>
-          <a:endParaRPr lang="en-US" b="0">
+          <a:endParaRPr lang="en-US">
             <a:effectLst/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr rtl="0"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -5416,27 +5414,31 @@
             </a:rPr>
             <a:t>Additionally, survey responses indicate that 60% of respondents said yes to a loyalty rewards program, with the remaining 40% expressing conditional interest depending on the rewards offered. Overall, no respondents were opposed to the program, with 80% preferring a points-based system over a punch-card style loyalty program.</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr rtl="0"/>
-          <a:endParaRPr lang="en-US" b="0">
+          <a:endParaRPr lang="en-US">
             <a:effectLst/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
+            <a:rPr lang="en-US">
               <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Results indicate that the top preferred reward is a points-based redemption system where customers earn one point for every dollar spent, with the opportunity to redeem points for free specialty drinks or food items. This aligns with purchase trends, as specialty coffee drinks and breakfast sandwiches are the most frequently ordered items.</a:t>
+            <a:t>Results indicate that the top preferred reward is a points-based redemption system where customers earn one point for every dollar spent, redeemable for free specialty drinks or food items. This aligns with purchase trends, as specialty coffee drinks and breakfast sandwiches are the most frequently ordered items.</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:pPr rtl="0"/>
@@ -6909,6 +6911,8 @@
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.53125" customWidth="1"/>
+    <col min="11" max="11" width="18.46484375" customWidth="1"/>
+    <col min="12" max="12" width="20.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">

--- a/week-01/Kuppi Coffee Company Customer Satisfaction Survey.xlsx
+++ b/week-01/Kuppi Coffee Company Customer Satisfaction Survey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sguer\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D715802-FD2B-4F9F-AD7B-E1EBC7A83B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BEA86C-4132-4424-AA3E-F79729F1562D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1208" yWindow="442" windowWidth="20025" windowHeight="12061" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="0" windowWidth="20025" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey_Responses" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>How often do you visit Kuppi Coffee?</t>
-  </si>
-  <si>
-    <t>How satisfied are you with your overall experience at our cafe? (1 = Very Dissatisfied → 5 = Very Satisfied)</t>
   </si>
   <si>
     <t>Which of the following do you typically order at Kuppi Coffee? (select all that apply)</t>
@@ -103,9 +100,6 @@
   </si>
   <si>
     <t>Food &amp; Drink Quality</t>
-  </si>
-  <si>
-    <t>How likely are you to recommend Kuppi Coffee to someone? (1 = Not at all likely → 10 = Extremely likely)</t>
   </si>
   <si>
     <t>Would you be interested in a loyalty/rewards program at Kuppi Coffee?</t>
@@ -144,9 +138,6 @@
     <t>Points-Based </t>
   </si>
   <si>
-    <t>Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Earn a free specialty drink after every 10 drink purchases;Earn a free pastry or baked good after every 6 food purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;</t>
-  </si>
-  <si>
     <t>Add more deals and discounts</t>
   </si>
   <si>
@@ -154,9 +145,6 @@
   </si>
   <si>
     <t>Specialty coffee drinks (lattes, mochas, cappuccinos, iced drinks, etc.);Breakfast sandwiches;Pastries &amp; baked goods;</t>
-  </si>
-  <si>
-    <t>Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty drink after every 10 drink purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;</t>
   </si>
   <si>
     <t>No</t>
@@ -171,16 +159,10 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;Earn a free specialty drink after every 10 drink purchases;Earn a free pastry or baked good after every 6 food purchases;</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
     <t>Specialty coffee drinks (lattes, mochas, cappuccinos, iced drinks, etc.);Pastries &amp; baked goods;</t>
-  </si>
-  <si>
-    <t>Earn a free specialty drink after every 10 drink purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;</t>
   </si>
   <si>
     <t xml:space="preserve">No additional comments or concerns at this time, but the next time I'm in town, I'm definitely coming here. </t>
@@ -190,9 +172,6 @@
   </si>
   <si>
     <t>Punch-Card </t>
-  </si>
-  <si>
-    <t>Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty drink after every 10 drink purchases;Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);</t>
   </si>
   <si>
     <t>Time to Complete</t>
@@ -253,6 +232,33 @@
   </si>
   <si>
     <t>Breakfast sandwiches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How likely are you to recommend Kuppi Coffee to someone? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">How satisfied are you with your overall experience at our cafe? </t>
+  </si>
+  <si>
+    <t>Points-Based</t>
+  </si>
+  <si>
+    <t>Earn 1 point for every $1, redeem 100 points for afree specialty drink or pastry of your choice;Earn a free specialty drink after every 10 drink purchases;Earn a free pastry or baked good after every 6 food purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;</t>
+  </si>
+  <si>
+    <t>Earn 1 point for every $1, redeem 100 points for afree specialty drink or pastry of your choice;Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty drink after every 10 drink purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;</t>
+  </si>
+  <si>
+    <t>Earn 1 point for every $1, redeem 100 points for afree specialty drink or pastry of your choice;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;Earn a free specialty drink after every 10 drink purchases;Earn a free pastry or baked good after every 6 food purchases;</t>
+  </si>
+  <si>
+    <t>Earn a free specialty drink after every 10 drink purchases;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);Earn 1 point for every $1, redeem 100 points for afree specialty drink or pastry of your choice;Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;</t>
+  </si>
+  <si>
+    <t>Punch-Card</t>
+  </si>
+  <si>
+    <t>Earn a free pastry or baked good after every 6 food purchases;Earn a free specialty drink after every 10 drink purchases;Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks;Earn 1 point for every $1, redeem 100 points for afree specialty drink or pastry of your choice;Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags);</t>
   </si>
 </sst>
 </file>
@@ -383,6 +389,127 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="42">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="28" formatCode="mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -525,111 +652,6 @@
       <alignment horizontal="left"/>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -669,13 +691,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -693,20 +708,11 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
@@ -2331,7 +2337,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -5675,6 +5681,127 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E202CC2-66D6-43A3-8832-B82793539121}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Interest in Loyalty Program">
+  <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="45" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="15"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Interest" fld="0" subtotal="count" baseField="15" baseItem="0"/>
+  </dataFields>
+  <formats count="9">
+    <format dxfId="13">
+      <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="15" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="10">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="8">
+      <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="15" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F16C2FB4-748C-49E0-B7CB-D09E4EAB8E0C}" name="PivotTable18" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="22" rowHeaderCaption="Type of Loyalty System">
   <location ref="A17:B20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -5740,35 +5867,35 @@
     <dataField name="Count of System" fld="17" subtotal="count" baseField="16" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="8">
+    <format dxfId="22">
       <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="21">
       <pivotArea dataOnly="0" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="20">
       <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="19">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="17">
       <pivotArea field="16" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="16" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5822,169 +5949,48 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8E202CC2-66D6-43A3-8832-B82793539121}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Interest in Loyalty Program">
-  <location ref="A1:B4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="45" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="15"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Interest" fld="0" subtotal="count" baseField="15" baseItem="0"/>
-  </dataFields>
-  <formats count="9">
-    <format dxfId="17">
-      <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="16">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="15">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="15" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="14">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="12">
-      <pivotArea field="15" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="11">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="15" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="10">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:S7" totalsRowCount="1" headerRowDxfId="41">
   <autoFilter ref="A1:S6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="21" xr3:uid="{574F5E68-45C2-4C0B-B4DD-7D02BE97E8A1}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="34">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="39" totalsRowDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="38" totalsRowDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{574F5E68-45C2-4C0B-B4DD-7D02BE97E8A1}" name="Time to Complete" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="1">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(D2:D6)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How often do you visit Kuppi Coffee?" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How satisfied are you with your overall experience at our cafe? (1 = Very Dissatisfied → 5 = Very Satisfied)" totalsRowFunction="custom" dataDxfId="31">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How often do you visit Kuppi Coffee?" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How satisfied are you with your overall experience at our cafe? " totalsRowFunction="custom" dataDxfId="34">
       <totalsRowFormula>AVERAGE(G2:G6)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Which of the following do you typically order at Kuppi Coffee? (select all that apply)" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Staff Friendliness" totalsRowFunction="custom" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Which of the following do you typically order at Kuppi Coffee? (select all that apply)" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Staff Friendliness" totalsRowFunction="custom" dataDxfId="32" totalsRowDxfId="0">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(I2:I6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Speed of Service" totalsRowFunction="custom" dataDxfId="27">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Speed of Service" totalsRowFunction="custom" dataDxfId="31">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(J2:J6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Cleanliness" totalsRowFunction="custom" dataDxfId="26">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Cleanliness" totalsRowFunction="custom" dataDxfId="30">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(K2:K6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Wi-Fi Quality" totalsRowFunction="custom" dataDxfId="25">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Wi-Fi Quality" totalsRowFunction="custom" dataDxfId="29">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(L2:L6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Seating Comfort" totalsRowFunction="custom" dataDxfId="24">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Seating Comfort" totalsRowFunction="custom" dataDxfId="28">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(M2:M6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Food &amp; Drink Quality" totalsRowFunction="custom" dataDxfId="23">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Food &amp; Drink Quality" totalsRowFunction="custom" dataDxfId="27">
       <totalsRowFormula array="1">AVERAGE(_xlfn.SWITCH(N2:N6,"Very Dissatisfied",1,"Dissatisfied",2,"Neutral",3,"Satisfied",4,"Very Satisfied",5))</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="How likely are you to recommend Kuppi Coffee to someone? (1 = Not at all likely → 10 = Extremely likely)" dataDxfId="22"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Would you be interested in a loyalty/rewards program at Kuppi Coffee?" totalsRowFunction="custom" dataDxfId="21">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="How likely are you to recommend Kuppi Coffee to someone? " dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Would you be interested in a loyalty/rewards program at Kuppi Coffee?" totalsRowFunction="custom" dataDxfId="4">
       <totalsRowFormula>COUNTIF(P2:P6, "Maybe, depending on the rewards")</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Would you prefer a punch-card style reward or a points-based system? (Please select one)" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Please rank the following rewards you would be most interested in (1 = most interest)" dataDxfId="19"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Any additional comments or concerns?" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Would you prefer a punch-card style reward or a points-based system? (Please select one)" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Please rank the following rewards you would be most interested in (1 = most interest)" dataDxfId="24"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Any additional comments or concerns?" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6336,7 +6342,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>3</v>
@@ -6345,43 +6351,43 @@
         <v>4</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>15</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="85.5" x14ac:dyDescent="0.45">
@@ -6399,49 +6405,49 @@
         <v>1.9097221957053989E-3</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G2" s="10">
         <v>5</v>
       </c>
       <c r="H2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="K2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>23</v>
-      </c>
       <c r="M2" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O2" s="10">
         <v>9</v>
       </c>
       <c r="P2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="S2" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="85.5" x14ac:dyDescent="0.45">
@@ -6459,49 +6465,49 @@
         <v>2.0949074023519643E-3</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G3" s="10">
         <v>5</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O3" s="10">
         <v>8</v>
       </c>
       <c r="P3" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="10" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="99.75" x14ac:dyDescent="0.45">
@@ -6519,49 +6525,49 @@
         <v>1.2847221951233223E-3</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G4" s="10">
         <v>5</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O4" s="10">
         <v>10</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="85.5" x14ac:dyDescent="0.45">
@@ -6579,49 +6585,49 @@
         <v>1.8402776986476965E-3</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G5" s="10">
         <v>5</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O5" s="10">
         <v>9</v>
       </c>
       <c r="P5" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q5" s="10" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="85.5" x14ac:dyDescent="0.45">
@@ -6639,49 +6645,49 @@
         <v>7.8703709732508287E-4</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G6" s="10">
         <v>5</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O6" s="10">
         <v>10</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q6" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="S6" s="8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.45">
@@ -6780,15 +6786,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="20">
         <v>2</v>
@@ -6796,7 +6802,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B3" s="20">
         <v>3</v>
@@ -6804,7 +6810,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="21" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B4" s="20">
         <v>5</v>
@@ -6812,15 +6818,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" s="22" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" s="21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" s="20">
         <v>4</v>
@@ -6828,7 +6834,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="21" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B19" s="20">
         <v>1</v>
@@ -6836,7 +6842,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="21" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B20" s="20">
         <v>5</v>
@@ -6844,15 +6850,15 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B35">
         <f>COUNTIF(Survey_Responses!R2:R6, "Earn a free specialty drink after every 10 drink purchases*")</f>
@@ -6861,7 +6867,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B36">
         <f>COUNTIF(Survey_Responses!R2:R6, "Earn a free pastry or baked good after every 6 food purchases*")</f>
@@ -6870,16 +6876,16 @@
     </row>
     <row r="37" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A37" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B37">
         <f>COUNTIF(Survey_Responses!R2:R6, "Earn 1 point for every $1, redeem 100 points for a free specialty drink or pastry of your choice*")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B38">
         <f>COUNTIF(Survey_Responses!R2:R6, "Earn a free specialty milk upgrade (oat, almond, macadamia) after every 10 drinks*")</f>
@@ -6888,7 +6894,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B39">
         <f>COUNTIF(Survey_Responses!R2:R6, "Redeem 200 points for exclusive Kuppi Coffee merch (cups, stationary, tote bags)*")</f>
@@ -6917,15 +6923,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B2">
         <f>COUNTIF(Survey_Responses!H2:H6, "*Drip Coffee*")</f>
@@ -6934,7 +6940,7 @@
     </row>
     <row r="3" spans="1:2" ht="57" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B3" s="16">
         <f>COUNTIF(Survey_Responses!H2:H6, "*Specialty coffee drinks (lattes, mochas, cappuccinos, iced drinks, etc.)*")</f>
@@ -6943,7 +6949,7 @@
     </row>
     <row r="4" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B4">
         <f>COUNTIF(Survey_Responses!H2:H6, "*Specialty non-coffee drinks (tea, chai, matcha, etc.)*")</f>
@@ -6952,7 +6958,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <f>COUNTIF(Survey_Responses!H2:H6, "*Breakfast sandwiches*")</f>
@@ -6961,7 +6967,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <f>COUNTIF(Survey_Responses!H2:H6, "*Pastries &amp; baked goods*")</f>
